--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,279 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125273671</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Motås, Motås, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>347166</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6537789</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125274640</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100188</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Motås, Motås, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>347165</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6537854</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,6 +1071,147 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125298007</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Motås, Motås, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>347200</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6537862</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Observerades i storvuxen äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125273671</v>
+        <v>125274640</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>100188</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,41 +816,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -864,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347166</v>
+        <v>347165</v>
       </c>
       <c r="R3" t="n">
-        <v>6537789</v>
+        <v>6537854</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125274640</v>
+        <v>125273671</v>
       </c>
       <c r="B4" t="n">
-        <v>100188</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,27 +948,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -991,13 +996,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347165</v>
+        <v>347166</v>
       </c>
       <c r="R4" t="n">
-        <v>6537854</v>
+        <v>6537789</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125274640</v>
+        <v>125273671</v>
       </c>
       <c r="B3" t="n">
-        <v>100188</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,27 +816,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -850,13 +864,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347165</v>
+        <v>347166</v>
       </c>
       <c r="R3" t="n">
-        <v>6537854</v>
+        <v>6537789</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125273671</v>
+        <v>125274640</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>100188</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,41 +957,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -996,13 +991,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347166</v>
+        <v>347165</v>
       </c>
       <c r="R4" t="n">
-        <v>6537789</v>
+        <v>6537854</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125274640</v>
+        <v>125273671</v>
       </c>
       <c r="B3" t="n">
-        <v>100188</v>
+        <v>58001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,27 +816,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -850,13 +864,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347165</v>
+        <v>347166</v>
       </c>
       <c r="R3" t="n">
-        <v>6537854</v>
+        <v>6537789</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125273671</v>
+        <v>125274640</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>100358</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,41 +957,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -996,13 +991,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347166</v>
+        <v>347165</v>
       </c>
       <c r="R4" t="n">
-        <v>6537789</v>
+        <v>6537854</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,7 +1076,7 @@
         <v>125298007</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>58001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -800,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125273671</v>
+        <v>125274640</v>
       </c>
       <c r="B3" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,41 +811,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -864,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347166</v>
+        <v>347165</v>
       </c>
       <c r="R3" t="n">
-        <v>6537789</v>
+        <v>6537854</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +890,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,15 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125274640</v>
+        <v>125273671</v>
       </c>
       <c r="B4" t="n">
-        <v>100358</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,27 +938,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -991,13 +986,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347165</v>
+        <v>347166</v>
       </c>
       <c r="R4" t="n">
-        <v>6537854</v>
+        <v>6537789</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,7 +1021,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1031,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,12 +1066,7 @@
         <v>125298007</v>
       </c>
       <c r="B5" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>125274640</v>
       </c>
       <c r="B3" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>125274640</v>
       </c>
       <c r="B3" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125273671</v>
       </c>
       <c r="B4" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125298007</v>
       </c>
       <c r="B5" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>80280120</v>
       </c>
       <c r="B2" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347116.8369518465</v>
+        <v>347117</v>
       </c>
       <c r="R2" t="n">
-        <v>6537735.389365803</v>
+        <v>6537735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +750,9 @@
           <t>2019-10-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125274640</v>
+        <v>125273671</v>
       </c>
       <c r="B3" t="n">
-        <v>100423</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,27 +796,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -845,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347165</v>
+        <v>347166</v>
       </c>
       <c r="R3" t="n">
-        <v>6537854</v>
+        <v>6537789</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,12 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125273671</v>
+        <v>125298007</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,11 +954,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>hane</t>
@@ -986,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347166</v>
+        <v>347200</v>
       </c>
       <c r="R4" t="n">
-        <v>6537789</v>
+        <v>6537862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,22 +1005,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Observerades i storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125298007</v>
+        <v>125274640</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,36 +1068,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1117,13 +1102,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347200</v>
+        <v>347165</v>
       </c>
       <c r="R5" t="n">
-        <v>6537862</v>
+        <v>6537854</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,27 +1132,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Observerades i storvuxen äldre granskog.</t>
+          <t>Fyndplatsen finns intill en klippvägg i storvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15201-2025 artfynd.xlsx
+++ b/artfynd/A 15201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80280120</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125273671</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1069,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125298007</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1181,8 +1201,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125274640</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>